--- a/Thesis Forecasting/PAPER CONTEXT/tables/picture_tables/P017_rbfnn_actual_vs_predicted_scatter.xlsx
+++ b/Thesis Forecasting/PAPER CONTEXT/tables/picture_tables/P017_rbfnn_actual_vs_predicted_scatter.xlsx
@@ -478,7 +478,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>appendix_materials/figures/appendix_I_testing_plots/error_analysis/rbfnn_actual_vs_predicted_scatter.png</t>
+          <t>PAPER CONTEXT/figures/appendix_I_testing_plots/error_analysis/rbfnn_actual_vs_predicted_scatter.png</t>
         </is>
       </c>
     </row>
@@ -537,7 +537,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>358.82</v>
+        <v>360.88</v>
       </c>
     </row>
     <row r="11">
